--- a/excel-files/LAS PINAS/GONZALO GATCHALIAN NATIONAL HIGH SCHOOL.xlsx
+++ b/excel-files/LAS PINAS/GONZALO GATCHALIAN NATIONAL HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29607"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="511" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F925E708-A22B-40BF-B211-4604577D6A66}"/>
+  <xr:revisionPtr revIDLastSave="586" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31402ACA-C591-47B4-96B4-47BA182B5DF3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5934,7 +5934,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="38.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -6006,7 +6006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -6078,7 +6078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -6222,7 +6222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6366,7 +6366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" ht="19.5">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6438,7 +6438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="12" spans="1:27" ht="19.5">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6510,7 +6510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J13" s="13"/>
       <c r="K13" s="7">
         <f>ROUNDDOWN(Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]] / 2, 0) * 2</f>
@@ -6527,7 +6527,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="38.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6599,7 +6599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6671,7 +6671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6815,7 +6815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6887,7 +6887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6959,7 +6959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" ht="19.5">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -7031,7 +7031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="19.5">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -7103,7 +7103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J22" s="13"/>
       <c r="K22" s="7">
         <f>ROUNDDOWN(Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]] / 2, 0) * 2</f>
@@ -7121,7 +7121,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="38.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -7193,7 +7193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -7265,7 +7265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7337,7 +7337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7409,7 +7409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7481,7 +7481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7553,7 +7553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7625,7 +7625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" ht="19.5">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7697,7 +7697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7769,7 +7769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J32" s="13"/>
       <c r="K32" s="7">
         <f>ROUNDDOWN(Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]] / 2, 0) * 2</f>
@@ -7787,7 +7787,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7859,7 +7859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7931,7 +7931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="19.5">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -8075,7 +8075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="38.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -8147,7 +8147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -8219,7 +8219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -8291,7 +8291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8363,7 +8363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8435,7 +8435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J42" s="13"/>
       <c r="K42" s="7">
         <f>ROUNDDOWN(Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]] / 2, 0) * 2</f>
@@ -8453,7 +8453,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8525,7 +8525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8597,7 +8597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8669,7 +8669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8741,7 +8741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8813,7 +8813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8885,7 +8885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8957,7 +8957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -9029,7 +9029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -9101,7 +9101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J52" s="13"/>
       <c r="K52" s="7">
         <f>ROUNDDOWN(Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]] / 2, 0) * 2</f>
@@ -9119,7 +9119,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -9191,7 +9191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" ht="19.5">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -9263,7 +9263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -9335,7 +9335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="38.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9479,7 +9479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9551,7 +9551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="19.5">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9623,7 +9623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9695,7 +9695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -10541,7 +10541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J72" s="13"/>
       <c r="K72" s="7">
         <f>ROUNDDOWN(Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]] / 2, 0) * 2</f>
@@ -11315,7 +11315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J82" s="13"/>
       <c r="K82" s="7">
         <f>ROUNDDOWN(Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]] / 2, 0) * 2</f>
@@ -12089,7 +12089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J92" s="13"/>
       <c r="K92" s="7">
         <f>ROUNDDOWN(Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]] / 2, 0) * 2</f>
@@ -14602,7 +14602,7 @@
       <c r="K127" s="5">
         <v>50</v>
       </c>
-      <c r="L127" s="29"/>
+      <c r="L127" s="1"/>
       <c r="M127" s="31"/>
       <c r="N127" s="5">
         <f t="shared" ref="N127" si="24">IF((J127-K127)&lt;0,0,(J127-K127))</f>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="P127" s="5"/>
       <c r="Q127" s="31"/>
-      <c r="R127" s="29"/>
+      <c r="R127" s="1"/>
       <c r="S127" s="31"/>
       <c r="T127" s="5">
         <f t="shared" si="18"/>
@@ -14629,7 +14629,7 @@
         <v>0</v>
       </c>
       <c r="W127" s="31"/>
-      <c r="X127" s="29"/>
+      <c r="X127" s="1"/>
       <c r="Y127" s="31"/>
       <c r="Z127" s="5">
         <f t="shared" si="20"/>
@@ -14671,7 +14671,7 @@
       <c r="K128" s="5">
         <v>50</v>
       </c>
-      <c r="L128" s="29"/>
+      <c r="L128" s="1"/>
       <c r="M128" s="31"/>
       <c r="N128" s="5">
         <f t="shared" ref="N128:N132" si="28">IF((J128-K128)&lt;0,0,(J128-K128))</f>
@@ -14683,7 +14683,7 @@
       </c>
       <c r="P128" s="5"/>
       <c r="Q128" s="31"/>
-      <c r="R128" s="29"/>
+      <c r="R128" s="1"/>
       <c r="S128" s="31"/>
       <c r="T128" s="5">
         <f t="shared" ref="T128:T132" si="30">IF((P128-Q128)&lt;0,0,(P128-Q128))</f>
@@ -14698,7 +14698,7 @@
         <v>0</v>
       </c>
       <c r="W128" s="31"/>
-      <c r="X128" s="29"/>
+      <c r="X128" s="1"/>
       <c r="Y128" s="31"/>
       <c r="Z128" s="5">
         <f t="shared" ref="Z128:Z132" si="32">IF((V128-W128)&lt;0,0,(V128-W128))</f>
@@ -14740,7 +14740,7 @@
       <c r="K129" s="5">
         <v>50</v>
       </c>
-      <c r="L129" s="29"/>
+      <c r="L129" s="1"/>
       <c r="M129" s="31"/>
       <c r="N129" s="5">
         <f t="shared" si="28"/>
@@ -14752,7 +14752,7 @@
       </c>
       <c r="P129" s="5"/>
       <c r="Q129" s="31"/>
-      <c r="R129" s="29"/>
+      <c r="R129" s="1"/>
       <c r="S129" s="31"/>
       <c r="T129" s="5">
         <f t="shared" si="30"/>
@@ -14767,7 +14767,7 @@
         <v>0</v>
       </c>
       <c r="W129" s="31"/>
-      <c r="X129" s="29"/>
+      <c r="X129" s="1"/>
       <c r="Y129" s="31"/>
       <c r="Z129" s="5">
         <f t="shared" si="32"/>
@@ -14801,7 +14801,7 @@
       <c r="K130" s="5">
         <v>50</v>
       </c>
-      <c r="L130" s="29"/>
+      <c r="L130" s="1"/>
       <c r="M130" s="31"/>
       <c r="N130" s="5">
         <f t="shared" si="28"/>
@@ -14813,7 +14813,7 @@
       </c>
       <c r="P130" s="5"/>
       <c r="Q130" s="31"/>
-      <c r="R130" s="29"/>
+      <c r="R130" s="1"/>
       <c r="S130" s="31"/>
       <c r="T130" s="5">
         <f t="shared" si="30"/>
@@ -14828,7 +14828,7 @@
         <v>0</v>
       </c>
       <c r="W130" s="31"/>
-      <c r="X130" s="29"/>
+      <c r="X130" s="1"/>
       <c r="Y130" s="31"/>
       <c r="Z130" s="5">
         <f t="shared" si="32"/>
@@ -14862,7 +14862,7 @@
       <c r="K131" s="5">
         <v>50</v>
       </c>
-      <c r="L131" s="29"/>
+      <c r="L131" s="1"/>
       <c r="M131" s="31"/>
       <c r="N131" s="5">
         <f t="shared" si="28"/>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="P131" s="5"/>
       <c r="Q131" s="31"/>
-      <c r="R131" s="29"/>
+      <c r="R131" s="1"/>
       <c r="S131" s="31"/>
       <c r="T131" s="5">
         <f t="shared" si="30"/>
@@ -14889,7 +14889,7 @@
         <v>0</v>
       </c>
       <c r="W131" s="31"/>
-      <c r="X131" s="29"/>
+      <c r="X131" s="1"/>
       <c r="Y131" s="31"/>
       <c r="Z131" s="5">
         <f t="shared" si="32"/>
@@ -14923,7 +14923,7 @@
       <c r="K132" s="5">
         <v>50</v>
       </c>
-      <c r="L132" s="29"/>
+      <c r="L132" s="1"/>
       <c r="M132" s="31"/>
       <c r="N132" s="5">
         <f t="shared" si="28"/>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="P132" s="5"/>
       <c r="Q132" s="31"/>
-      <c r="R132" s="29"/>
+      <c r="R132" s="1"/>
       <c r="S132" s="31"/>
       <c r="T132" s="5">
         <f t="shared" si="30"/>
@@ -14950,7 +14950,7 @@
         <v>0</v>
       </c>
       <c r="W132" s="31"/>
-      <c r="X132" s="29"/>
+      <c r="X132" s="1"/>
       <c r="Y132" s="31"/>
       <c r="Z132" s="5">
         <f t="shared" si="32"/>
@@ -15144,7 +15144,7 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C126 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 H103:I110 Q103:R110 W103:X110 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K103:L110 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 N3:R3 Y13 K63:L71 K73:L81 K83:L91 K93:L101 H112:I132 N127:R132 W112:X132 T13:V132 J6:J132 Z4:AA132 K112:L132 D103:F110 D112:F132" name="LAS"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 D23:F31 D33:F41 H33:I41 D43:F51 H43:I51 D53:F61 H53:I61 D63:F71 H63:I71 D73:F81 H73:I81 D83:F91 H83:I91 D93:F101 H93:I101 H103:I110 W103:X110 H14:I21 H23:I31 H6:I12 Q112:R112 P2:R2 V2:X3 N13:P126 D5:F12 N4:P4 T4:V4 J4 N3:R3 Y13 H112:I132 N127:Q132 T13:V132 J6:J132 Z4:AA132 D103:F110 D112:F132 K6:L12 K14:L21 K23:L31 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L132 N5:R12 Q63:R71 Q103:R110 Q14:R21 Q23:R31 Q33:R41 Q43:R51 Q53:R61 Q73:R81 Q83:R91 Q93:R101 Q113:Q126 R113:R132 T5:X12 W63:X71 W33:X41 W43:X51 W53:X61 W73:X81 W83:X91 W93:X101 W23:X31 W14:X21 W112:X132" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 M14:M110 M112:M132 S112:S132 Y112:Y132 G103:G110 G112:G132" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -15154,15 +15154,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M112:M132 Y112:Y132 S112:S132 G112:G132" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L53:L61 L73:L81 L83:L91 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 L112:L132 R103:R110 L103:L110 X103:X110 L93:L101 X112:X132 R112:R132 F103:F110 F112:F132" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F43:F51 F63:F71 F73:F81 F93:F101 F83:F91 F23:F31 F5:F12 F103:F110 F112:F132 F33:F41 F53:F61 X103:X110 F14:F21" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L132 R103:R110 R53:R61 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R83:R91 R93:R101 R112:R132 X53:X61 X93:X101 X33:X41 X43:X51 X63:X71 X73:X81 X83:X91 X23:X31 X5:X12 X14:X21 X112:X132" xr:uid="{32C1021F-D383-4E8F-BA04-95834989D573}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15324,7 +15327,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="19.149999999999999">
+    <row r="3" spans="1:27" ht="38.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -15393,7 +15396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.149999999999999">
+    <row r="4" spans="1:27" ht="19.5">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -15462,7 +15465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999">
+    <row r="5" spans="1:27" ht="19.5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -15531,7 +15534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999">
+    <row r="6" spans="1:27" ht="19.5">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -15600,7 +15603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999">
+    <row r="7" spans="1:27" ht="19.5">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -15669,7 +15672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999">
+    <row r="8" spans="1:27" ht="19.5">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -15738,7 +15741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999">
+    <row r="9" spans="1:27" ht="19.5">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -15807,7 +15810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999">
+    <row r="10" spans="1:27" ht="19.5">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -15876,8 +15879,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1"/>
-    <row r="12" spans="1:27" ht="19.149999999999999">
+    <row r="11" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="12" spans="1:27" ht="38.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -15946,7 +15949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999">
+    <row r="13" spans="1:27" ht="19.5">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -16015,7 +16018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999">
+    <row r="14" spans="1:27" ht="19.5">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -16084,7 +16087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999">
+    <row r="15" spans="1:27" ht="19.5">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -16153,7 +16156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999">
+    <row r="16" spans="1:27" ht="19.5">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -16222,7 +16225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -16291,7 +16294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999">
+    <row r="18" spans="1:27" ht="19.5">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -16360,7 +16363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -16429,8 +16432,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="20" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="21" spans="1:27" ht="38.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -16499,7 +16502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999">
+    <row r="22" spans="1:27" ht="19.5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -16568,7 +16571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="19.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -16637,7 +16640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -16706,7 +16709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -16775,7 +16778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -16844,7 +16847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -16913,7 +16916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -16982,7 +16985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -17051,8 +17054,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1"/>
-    <row r="31" spans="1:27" ht="19.149999999999999">
+    <row r="30" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="31" spans="1:27" ht="19.5">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -17121,7 +17124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999">
+    <row r="32" spans="1:27" ht="19.5">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -17190,7 +17193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -17259,7 +17262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -17328,7 +17331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="38.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -17397,7 +17400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -17466,7 +17469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="19.5">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -17535,7 +17538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -17604,7 +17607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -17673,7 +17676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -17742,7 +17745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -17811,8 +17814,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1"/>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -17881,7 +17884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -17950,7 +17953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -18019,7 +18022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -18088,7 +18091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -18157,7 +18160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -18226,7 +18229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -18295,7 +18298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -18364,7 +18367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -18433,7 +18436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999">
+    <row r="52" spans="1:27" ht="19.5">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -18502,7 +18505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -18571,8 +18574,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.149999999999999">
+    <row r="54" spans="1:27" s="7" customFormat="1" ht="15"/>
+    <row r="55" spans="1:27" ht="19.5">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -18641,7 +18644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999">
+    <row r="56" spans="1:27" ht="19.5">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -18710,7 +18713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999">
+    <row r="57" spans="1:27" ht="19.5">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -18779,7 +18782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999">
+    <row r="58" spans="1:27" ht="19.5">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -18848,7 +18851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999">
+    <row r="59" spans="1:27" ht="38.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -18917,7 +18920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999">
+    <row r="60" spans="1:27" ht="19.5">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -18986,7 +18989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999">
+    <row r="61" spans="1:27" ht="19.5">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -19055,7 +19058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999">
+    <row r="62" spans="1:27" ht="19.5">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -19124,7 +19127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="19.5">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -19193,7 +19196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="19.5">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -19262,7 +19265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="19.5">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -20113,7 +20116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
+    <row r="78" spans="1:27" s="7" customFormat="1" ht="15"/>
     <row r="79" spans="1:27" ht="19.5">
       <c r="A79" s="10">
         <v>8</v>
@@ -20895,7 +20898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1"/>
+    <row r="90" spans="1:27" s="7" customFormat="1" ht="15"/>
     <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
@@ -21677,7 +21680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="15"/>
     <row r="103" spans="1:27" ht="19.5">
       <c r="A103" s="10">
         <v>10</v>
@@ -22459,8 +22462,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1"/>
-    <row r="115" spans="1:28" ht="38.450000000000003">
+    <row r="114" spans="1:28" s="7" customFormat="1" ht="15"/>
+    <row r="115" spans="1:28" ht="38.25">
       <c r="A115" s="1" t="s">
         <v>24</v>
       </c>
@@ -22529,7 +22532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.149999999999999">
+    <row r="116" spans="1:28" ht="19.5">
       <c r="A116" s="1" t="s">
         <v>24</v>
       </c>
@@ -22598,7 +22601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.149999999999999">
+    <row r="117" spans="1:28" ht="19.5">
       <c r="A117" s="1" t="s">
         <v>24</v>
       </c>
@@ -22667,7 +22670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.149999999999999">
+    <row r="118" spans="1:28" ht="19.5">
       <c r="A118" s="1" t="s">
         <v>24</v>
       </c>
@@ -22736,7 +22739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.450000000000003">
+    <row r="119" spans="1:28" ht="38.25">
       <c r="A119" s="1" t="s">
         <v>24</v>
       </c>
@@ -22805,7 +22808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="19.149999999999999">
+    <row r="120" spans="1:28" ht="38.25">
       <c r="A120" s="1" t="s">
         <v>24</v>
       </c>
@@ -22874,7 +22877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="57.75">
       <c r="A121" s="1" t="s">
         <v>24</v>
       </c>
@@ -22943,7 +22946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>24</v>
       </c>
@@ -23706,7 +23709,7 @@
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C115:C122 C67:C77 C79:C89 C91:C101 C103:C113" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
+    <protectedRange sqref="J2:L2 N3:O10 T3:U10 Z3:AA10 Z12:AA19 Z21:AA29 Z31:AA41 Z43:AA53 Z55:AA65 Z67:AA77 Z79:AA89 Z91:AA101 Z103:AA113 Z115:AA122 D67:F77 D115:F122 D103:F113 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D79:F89 D91:F101 D2:F10 H3:L10 H67:L77 H115:L122 H103:L113 H12:L19 H21:L29 H31:L41 H43:L53 H55:L65 H79:L89 H91:L101 P2:R10 N67:R77 N115:R122 N103:R113 N12:R19 N21:R29 N31:R41 N43:R53 N55:R65 N79:R89 N91:R101 T67:X77 T115:X122 T103:X113 T12:X19 T21:X29 T31:X41 T43:X53 T55:X65 T79:X89 T91:X101 V2:X10" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -23716,12 +23719,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F103:F113 F115:F122 F55:F65 F91:F101 F12:F19 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F3:F10 L103:L113 L115:L122 L55:L65 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L91:L101 R103:R113 R115:R122 R55:R65 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R91:R101 X103:X113 X55:X65 X91:X101 X12:X19 X21:X29 X31:X41 X43:X53 X67:X77 X79:X89" xr:uid="{8633B697-4340-45E1-9FD5-53DA89586F5D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
